--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553E365B-A93E-4276-A9D7-76F2B9EE1B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3664EEC-650E-412B-A9F5-AAC03C764DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21945" yWindow="5055" windowWidth="19515" windowHeight="11610" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
+    <workbookView xWindow="-28920" yWindow="1050" windowWidth="29040" windowHeight="15720" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Links" sheetId="1" r:id="rId1"/>
+    <sheet name="Kafka Self Service" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -198,6 +199,30 @@
   </si>
   <si>
     <t xml:space="preserve">Kafka self service code </t>
+  </si>
+  <si>
+    <t>https://it-insights.rewe.local/overview?search=sst2799</t>
+  </si>
+  <si>
+    <t>IT insights</t>
+  </si>
+  <si>
+    <t>Kafka self service</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>https://code.dev.rewe.cloud/ip/caas/custom-images/kafka-self-service-gitlab-image</t>
+  </si>
+  <si>
+    <t>This is the repo used for building the Kafka Self Service Docker image. It will download the latest go code and it will then push the docker image to the Docker Registry</t>
+  </si>
+  <si>
+    <t>This repo contains the definition of the Gitlab pipeline</t>
+  </si>
+  <si>
+    <t>https://code.dev.rewe.cloud/ip/caas/kafka-self-service-pipeline</t>
   </si>
 </sst>
 </file>
@@ -266,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -288,6 +313,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -307,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}" name="Table3" displayName="Table3" ref="A3:C14" totalsRowShown="0">
-  <autoFilter ref="A3:C14" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}" name="Table3" displayName="Table3" ref="A3:C15" totalsRowShown="0">
+  <autoFilter ref="A3:C15" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{92DEE286-5F23-49AE-A993-EE800877A5EE}" name="Title"/>
     <tableColumn id="2" xr3:uid="{16826D26-E8CF-4027-A8E6-28B0A1A1041D}" name="URL" dataCellStyle="Hyperlink"/>
@@ -635,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51094AFD-03E5-4E2E-A855-873D3CEE7610}">
-  <dimension ref="A3:C14"/>
+  <dimension ref="A3:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -743,6 +771,14 @@
       </c>
       <c r="B14" s="3" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -764,4 +800,52 @@
     <tablePart r:id="rId12"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A03D07D-390D-4964-84B8-DA4DC0A69C33}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="62.08984375" customWidth="1"/>
+    <col min="2" max="2" width="73.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{0C302664-FE7C-45B4-B81E-F297190B1C6D}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{6ECA404E-1699-4097-B9D5-BCF71406C79C}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{FD83F1CF-F75B-4B95-8D92-29CEF8DC3234}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3664EEC-650E-412B-A9F5-AAC03C764DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB9DCB9-5910-4813-A7C7-9A3AE88246CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1050" windowWidth="29040" windowHeight="15720" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
     <sheet name="Kafka Self Service" sheetId="2" r:id="rId2"/>
+    <sheet name="RTP" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -90,9 +91,6 @@
     <t>Kafka Self-Service</t>
   </si>
   <si>
-    <t>https://code.dev.rewe.cloud/ip/caas/kafka-self-service</t>
-  </si>
-  <si>
     <t>https://rewe.atlassian.net/wiki/spaces/GBOS/pages/1260465890/Use+REWE+Kafka+topic+naming+convention</t>
   </si>
   <si>
@@ -223,6 +221,22 @@
   </si>
   <si>
     <t>https://code.dev.rewe.cloud/ip/caas/kafka-self-service-pipeline</t>
+  </si>
+  <si>
+    <t>Ulbrich, Robert: https://gitlab.cicd.rewe.cloud/rewe-tech-platform/prod633/applica... | Provisioning of Mirrormakers for RTP | Microsoft Teams</t>
+  </si>
+  <si>
+    <t>https://gitlab.cicd.rewe.cloud/rewe-tech-platform/prod633/applications/kafka-test/kafka-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTP </t>
+  </si>
+  <si>
+    <t>Engineer on duty</t>
+  </si>
+  <si>
+    <t>https://code.dev.rewe.cloud/ip/caas/kafka-self-service
+https://code.dev.rewe.cloud/ip/caas/kafka-self-service/-/merge_requests</t>
   </si>
 </sst>
 </file>
@@ -291,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -315,6 +329,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -668,23 +691,23 @@
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -700,10 +723,10 @@
     </row>
     <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -730,55 +753,58 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -787,17 +813,18 @@
     <hyperlink ref="B7" r:id="rId2" xr:uid="{73492074-DA97-44C4-90AF-C79CF5DBA21C}"/>
     <hyperlink ref="B8" r:id="rId3" xr:uid="{EB59DAC2-E5D5-4D34-943B-42B2CB5423FF}"/>
     <hyperlink ref="B9" r:id="rId4" xr:uid="{4E33CBEF-9533-48D2-BC67-45717AA3FBEB}"/>
-    <hyperlink ref="B10" r:id="rId5" xr:uid="{05DBEA20-3695-490C-93E6-102AAED9E6DE}"/>
+    <hyperlink ref="B10" r:id="rId5" display="https://code.dev.rewe.cloud/ip/caas/kafka-self-service" xr:uid="{05DBEA20-3695-490C-93E6-102AAED9E6DE}"/>
     <hyperlink ref="B11" r:id="rId6" xr:uid="{A82AE5B1-B074-4F20-A1EE-F4A97F50477A}"/>
     <hyperlink ref="B12" r:id="rId7" xr:uid="{4233B4E2-FA5D-4231-82C5-0DEBEE98C968}"/>
     <hyperlink ref="B13" r:id="rId8" xr:uid="{F04C5879-D231-445B-930D-ECD231A12A54}"/>
     <hyperlink ref="B14" r:id="rId9" xr:uid="{5A6AE6C9-548A-4156-8643-080D848DAC3C}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{67284D87-5311-488E-912B-0A02FF85032A}"/>
+    <hyperlink ref="B5" r:id="rId11" xr:uid="{997FA379-5083-4A11-A6D1-809BA5407CED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
   <tableParts count="1">
-    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -813,31 +840,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -848,4 +875,33 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C234A6A-5C6C-4377-8976-D599C42620F0}">
+  <dimension ref="E3:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" display="https://teams.microsoft.com/l/message/19:meeting_NWM2NjU4MGItN2JhMy00NGJiLWEwOTItNmNhOTc5ZTUxMzY3@thread.v2/1772458060267?context=%7B%22contextType%22%3A%22chat%22%7D" xr:uid="{090EFF01-141B-4203-9C19-FEAA5A9787AA}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{2FAFDE5F-C7BC-44D2-B43D-3A7B95C1978C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB9DCB9-5910-4813-A7C7-9A3AE88246CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B7F094-9F14-4C8F-BD17-A0FCC275DCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1050" windowWidth="29040" windowHeight="15720" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
+    <workbookView xWindow="-28920" yWindow="1050" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
     <sheet name="Kafka Self Service" sheetId="2" r:id="rId2"/>
     <sheet name="RTP" sheetId="3" r:id="rId3"/>
+    <sheet name="Change control" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -237,6 +238,15 @@
   <si>
     <t>https://code.dev.rewe.cloud/ip/caas/kafka-self-service
 https://code.dev.rewe.cloud/ip/caas/kafka-self-service/-/merge_requests</t>
+  </si>
+  <si>
+    <t>https://servicedesk.eil.risnet.de/browse/CHANGE-3763</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/l/message/19:meeting_ODFhYWYxOWYtMjAwMC00MjgyLTliNjItOTZkNjU2Y2IzNmE2@thread.v2/1772627431981?context=%7B%22contextType%22%3A%22chat%22%7D</t>
+  </si>
+  <si>
+    <t>O&amp;M migration</t>
   </si>
 </sst>
 </file>
@@ -355,6 +365,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>344054</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>105623</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A321B2-EAC1-E41F-5B01-12E88BEE826D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8268854" cy="6077798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -904,4 +963,34 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF4F27D-A951-431B-81D5-DDDFCFE35034}">
+  <dimension ref="O11:O13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="11" spans="15:15" x14ac:dyDescent="0.35">
+      <c r="O11" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="15:15" x14ac:dyDescent="0.35">
+      <c r="O12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="15:15" x14ac:dyDescent="0.35">
+      <c r="O13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O11" r:id="rId1" xr:uid="{4AB133D0-16BC-4751-927B-F13972E7426F}"/>
+    <hyperlink ref="O13" r:id="rId2" xr:uid="{0C18E59B-8920-4BF4-A56A-04786EB994F8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B7F094-9F14-4C8F-BD17-A0FCC275DCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B55E587-603C-43A5-B19E-B423DD2349AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1050" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
+    <workbookView xWindow="-21945" yWindow="5055" windowWidth="19515" windowHeight="11610" activeTab="1" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>O&amp;M migration</t>
+  </si>
+  <si>
+    <t>https://it-insights-api.rewe.local/swagger-ui/index.html</t>
+  </si>
+  <si>
+    <t>IT insight API</t>
   </si>
 </sst>
 </file>
@@ -879,18 +885,19 @@
     <hyperlink ref="B14" r:id="rId9" xr:uid="{5A6AE6C9-548A-4156-8643-080D848DAC3C}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{67284D87-5311-488E-912B-0A02FF85032A}"/>
     <hyperlink ref="B5" r:id="rId11" xr:uid="{997FA379-5083-4A11-A6D1-809BA5407CED}"/>
+    <hyperlink ref="B15" r:id="rId12" xr:uid="{3F6F8243-51FF-46D2-9E1F-36AA9EE212C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A03D07D-390D-4964-84B8-DA4DC0A69C33}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62.08984375" customWidth="1"/>
@@ -926,11 +933,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{0C302664-FE7C-45B4-B81E-F297190B1C6D}"/>
     <hyperlink ref="B6" r:id="rId2" xr:uid="{6ECA404E-1699-4097-B9D5-BCF71406C79C}"/>
     <hyperlink ref="B7" r:id="rId3" xr:uid="{FD83F1CF-F75B-4B95-8D92-29CEF8DC3234}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{9EE5D787-F140-4202-BA2B-C8A2446AD6E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B55E587-603C-43A5-B19E-B423DD2349AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D58F5-AA74-4385-84BC-BA2B51E978C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21945" yWindow="5055" windowWidth="19515" windowHeight="11610" activeTab="1" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
+    <workbookView xWindow="-22860" yWindow="4515" windowWidth="19515" windowHeight="11610" activeTab="1" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -253,6 +253,10 @@
   </si>
   <si>
     <t>IT insight API</t>
+  </si>
+  <si>
+    <t>change .gitlab-ci.yml updating the version
+change README.md</t>
   </si>
 </sst>
 </file>
@@ -321,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -354,6 +358,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -897,19 +904,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A03D07D-390D-4964-84B8-DA4DC0A69C33}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62.08984375" customWidth="1"/>
     <col min="2" max="2" width="73.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -917,15 +925,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -933,7 +944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>42</v>
       </c>

--- a/SEVEN_Kakfa_Links.xlsx
+++ b/SEVEN_Kakfa_Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A233C1F\Documents\Docs&amp;Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D58F5-AA74-4385-84BC-BA2B51E978C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4B2B8E-CA6A-46B4-9309-B2AFE6D7B97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="4515" windowWidth="19515" windowHeight="11610" activeTab="1" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
+    <workbookView xWindow="-20655" yWindow="3675" windowWidth="19185" windowHeight="11265" xr2:uid="{9D751822-9D83-4D60-B2B6-9E7CF2D78AD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>https://rewe.atlassian.net/wiki/spaces/TITISEVEN/pages/1134952479/System+overview+Kafka+Clusters+managed+by+Team+SEVEN</t>
   </si>
@@ -257,6 +257,12 @@
   <si>
     <t>change .gitlab-ci.yml updating the version
 change README.md</t>
+  </si>
+  <si>
+    <t>https://github.com/rewe-digital-platform/saas-kafka-self-service/</t>
+  </si>
+  <si>
+    <t>O&amp;M saas repo</t>
   </si>
 </sst>
 </file>
@@ -430,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}" name="Table3" displayName="Table3" ref="A3:C15" totalsRowShown="0">
-  <autoFilter ref="A3:C15" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}" name="Table3" displayName="Table3" ref="A3:C16" totalsRowShown="0">
+  <autoFilter ref="A3:C16" xr:uid="{4FEFBF19-B0BB-4FF9-82D1-B22F0F681040}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{92DEE286-5F23-49AE-A993-EE800877A5EE}" name="Title"/>
     <tableColumn id="2" xr3:uid="{16826D26-E8CF-4027-A8E6-28B0A1A1041D}" name="URL" dataCellStyle="Hyperlink"/>
@@ -758,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51094AFD-03E5-4E2E-A855-873D3CEE7610}">
-  <dimension ref="A3:C15"/>
+  <dimension ref="A3:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -877,6 +883,14 @@
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -893,11 +907,12 @@
     <hyperlink ref="B6" r:id="rId10" xr:uid="{67284D87-5311-488E-912B-0A02FF85032A}"/>
     <hyperlink ref="B5" r:id="rId11" xr:uid="{997FA379-5083-4A11-A6D1-809BA5407CED}"/>
     <hyperlink ref="B15" r:id="rId12" xr:uid="{3F6F8243-51FF-46D2-9E1F-36AA9EE212C8}"/>
+    <hyperlink ref="B16" r:id="rId13" xr:uid="{F8618F85-9977-4563-AF67-F876A4278094}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
